--- a/data/trans_orig/IP07KS_C04_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C04_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse solo/a en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de sentirse solo/a, percibida por el/la menor [KIDSCREEN 10] en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -1064,69 +1064,69 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>657</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>55,25%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1172,74 +1172,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>43,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>44,75%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>513</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>575</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2523</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3006</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1628,107 +1628,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1596</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5661</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>1596</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5265</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>5372</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17637</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10134</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>28611</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>32,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>33342</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8967</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>54403</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>53,9%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>87,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19124</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30641</t>
+          <t>16823</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>52466</t>
+          <t>26844</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27117</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85495</t>
+          <t>37903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>40,81%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36179</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25246</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43491</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>46,42%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>26993</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7358</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>50430</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>43,64%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37972</t>
+          <t>27677</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26621</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45873</t>
+          <t>32480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>64964</t>
+          <t>63855</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32883</t>
+          <t>52846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89089</t>
+          <t>73951</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>79,63%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,107 +2084,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3954</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2952</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>597</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>350</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>463</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19396</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>15863</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>21674</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>84,05%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>68,74%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>16499</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>13066</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18956</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>79,06%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>62,61%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>16527</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17217</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23587</t>
+          <t>19011</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>37844</t>
+          <t>35924</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33094</t>
+          <t>31076</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41469</t>
+          <t>39089</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -3105,107 +3105,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1796</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>9441</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1849</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>8524</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>47,8%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1796</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>9593</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>15582</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>8560</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>89,4%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>49,11%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>17954</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>10309</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>19750</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>90,91%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,27 +3293,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>20603</t>
+          <t>18520</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,107 +3448,107 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>841</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>860</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>4087</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>4565</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>20,45%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>860</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>5381</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -3561,107 +3561,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>3549</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2782</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>24,15%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>17,87%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>2716</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>2661</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>541</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>3995</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>7379</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>19,7%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>36,38%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>1348</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>6655</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>45,28%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>14863</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>11124</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>17427</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>73,27%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>54,84%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>10054</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>7012</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>12440</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>68,41%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>47,71%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>84,64%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>24592</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>20879</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>29503</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,107 +4130,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>479</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>1154</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>3775</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>19,41%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>3009</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3511</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>1159</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>4147</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>553</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2590</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>6216</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>13,31%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>31,95%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>3098</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1126</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>6297</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>34,17%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -4582,72 +4582,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>15228</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>11534</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>17598</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>78,29%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>59,3%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>14817</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>11302</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>16837</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>80,42%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>61,34%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>17677</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>31516</t>
+          <t>30835</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>26836</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>34772</t>
+          <t>34015</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>87,63%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4925,107 +4925,107 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>1179</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>3777</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5231</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>18,14%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>5432</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>1179</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>4662</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>4576</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>1749</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>9147</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>2225</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>4408</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>1684</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>9658</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10405</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11965</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>6149</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>21934</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>25,16%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>12,93%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>46,12%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>4994</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>9317</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>18,3%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>34,14%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>21338</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>27715</t>
+          <t>29160</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>31017</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>22202</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>37354</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>65,22%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>46,68%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>78,54%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>20700</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>16271</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>23858</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>75,84%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>59,61%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>87,41%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>29883</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>36885</t>
+          <t>25648</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>50583</t>
+          <t>52977</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>40339</t>
+          <t>42458</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>57928</t>
+          <t>60602</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,72 +5494,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>4495</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>3234</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>7547</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>11,88%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -5607,72 +5607,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>5570</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>6,38%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2707</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>7039</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -5720,72 +5720,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>10509</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>5160</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>17392</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>12,04%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>19,93%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>5048</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>2086</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>9790</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>15,42%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>9825</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>22138</t>
+          <t>25525</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -5833,72 +5833,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>50771</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>40881</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>59184</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>46,86%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>67,83%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>34720</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>27327</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>41588</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>54,67%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>43,03%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>65,49%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>46654</t>
+          <t>38135</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>36891</t>
+          <t>29490</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>54249</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>81373</t>
+          <t>88906</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>70485</t>
+          <t>77405</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>92175</t>
+          <t>100287</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,62%</t>
         </is>
       </c>
     </row>
@@ -5946,72 +5946,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>24126</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>17051</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>33553</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>27,65%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>19,54%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>38,46%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>17795</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>12546</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>24303</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>28,02%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>38,27%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>16843</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>31882</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>41067</t>
+          <t>43912</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>31849</t>
+          <t>33486</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>51616</t>
+          <t>55156</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>12423</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>4416</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>1428</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>9614</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>18860</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>11612</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>28554</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>9835</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>5338</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>16713</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>38246</t>
+          <t>40997</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -6515,72 +6515,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>91110</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>73827</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>109547</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>33,73%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>27,33%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>40,56%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>82250</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>58789</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>129707</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>39,08%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>61,63%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>88892</t>
+          <t>62013</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>71467</t>
+          <t>51047</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>105912</t>
+          <t>75555</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>171142</t>
+          <t>153123</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>144736</t>
+          <t>131210</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>229586</t>
+          <t>172989</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -6628,72 +6628,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>156391</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>138290</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>173545</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>57,9%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>64,25%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>110014</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>69990</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>130953</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>52,27%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>33,25%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>62,22%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>161662</t>
+          <t>115647</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>142272</t>
+          <t>103072</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>182435</t>
+          <t>127424</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>271676</t>
+          <t>272038</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>224279</t>
+          <t>250450</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>297525</t>
+          <t>296114</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
